--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T11:09:51+00:00</t>
+    <t>2022-10-04T14:18:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T14:18:04+00:00</t>
+    <t>2022-10-04T19:52:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T19:52:49+00:00</t>
+    <t>2022-10-04T20:54:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T20:54:27+00:00</t>
+    <t>2022-10-11T09:25:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -250,53 +250,53 @@
 </t>
   </si>
   <si>
+    <t>Extension.id</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Extension.extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Extension.id</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Extension.extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Extension.url</t>
@@ -887,7 +887,7 @@
         <v>77</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AJ2" t="s" s="2">
         <v>74</v>
@@ -895,7 +895,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
@@ -906,25 +906,25 @@
         <v>75</v>
       </c>
       <c r="F3" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="G3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="L3" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -975,13 +975,13 @@
         <v>74</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF3" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
         <v>74</v>
@@ -990,12 +990,12 @@
         <v>74</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
@@ -1018,13 +1018,13 @@
         <v>74</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K4" t="s" s="2">
         <v>29</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
@@ -1063,19 +1063,19 @@
         <v>74</v>
       </c>
       <c r="AA4" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AB4" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="AB4" t="s" s="2">
+      <c r="AC4" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD4" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AC4" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD4" t="s" s="2">
+      <c r="AE4" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="AE4" t="s" s="2">
-        <v>92</v>
       </c>
       <c r="AF4" t="s" s="2">
         <v>75</v>
@@ -1087,7 +1087,7 @@
         <v>74</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>74</v>
@@ -1103,10 +1103,10 @@
       </c>
       <c r="D5" s="2"/>
       <c r="E5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
         <v>74</v>
@@ -1180,10 +1180,10 @@
         <v>93</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
         <v>74</v>
@@ -1208,7 +1208,7 @@
         <v>75</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>74</v>
@@ -1283,7 +1283,7 @@
         <v>75</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
         <v>74</v>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-11T09:25:49+00:00</t>
+    <t>2022-10-21T11:28:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Extension for the last date a condition was confirmed valid with its current clinical- and verification status, stage and severity, typically the last performed follow-up</t>
+    <t>Extension for the last date a Condition-instance was confirmed valid in its current state. E.g. with its current clinical- and verification status, stage and severity. Typically the last performed follow-up</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-21T11:28:25+00:00</t>
+    <t>2022-10-21T11:53:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-21T11:53:19+00:00</t>
+    <t>2022-10-24T14:23:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-24T14:23:47+00:00</t>
+    <t>2022-10-24T22:55:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-24T22:55:30+00:00</t>
+    <t>2022-11-07T08:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-07T08:18:22+00:00</t>
+    <t>2022-11-07T15:10:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-07T15:10:04+00:00</t>
+    <t>2022-11-08T22:20:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-08T22:20:55+00:00</t>
+    <t>2022-11-08T22:23:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-08T22:23:46+00:00</t>
+    <t>2022-11-30T21:48:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-30T21:48:52+00:00</t>
+    <t>2022-12-01T00:22:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-01T00:22:19+00:00</t>
+    <t>2022-12-01T21:15:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-01T21:15:09+00:00</t>
+    <t>2022-12-05T08:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T08:13:32+00:00</t>
+    <t>2022-12-05T08:52:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T08:52:10+00:00</t>
+    <t>2022-12-05T08:58:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T08:58:17+00:00</t>
+    <t>2022-12-05T09:15:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="106">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T09:15:32+00:00</t>
+    <t>2023-04-18T12:02:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -129,6 +129,9 @@
     <t>element:Element</t>
   </si>
   <si>
+    <t>ID</t>
+  </si>
+  <si>
     <t>Path</t>
   </si>
   <si>
@@ -244,6 +247,10 @@
   </si>
   <si>
     <t>*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -642,45 +649,45 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.59765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.66015625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="6.77734375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.26171875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="14.4453125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="19.59765625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="37.17578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="10.04296875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.26953125" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="15.6640625" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="19.625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.4140625" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="18.1875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="11.0390625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="13.875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="19.625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="18.1875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="36" max="36" width="24.98046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="24.98046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -792,93 +799,96 @@
       <c r="AJ1" t="s" s="1">
         <v>73</v>
       </c>
+      <c r="AK1" t="s" s="1">
+        <v>74</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="E2" t="s" s="2">
-        <v>75</v>
-      </c>
+      <c r="B2" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K2" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L2" t="s" s="2">
         <v>7</v>
       </c>
-      <c r="L2" t="s" s="2">
+      <c r="M2" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="M2" s="2"/>
       <c r="N2" s="2"/>
-      <c r="O2" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="P2" s="2"/>
-      <c r="Q2" t="s" s="2">
-        <v>74</v>
-      </c>
+      <c r="O2" s="2"/>
+      <c r="P2" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AE2" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF2" t="s" s="2">
         <v>29</v>
-      </c>
-      <c r="AF2" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>76</v>
@@ -887,412 +897,427 @@
         <v>77</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="AK2" t="s" s="2">
+        <v>75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="K3" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L3" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="M3" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q3" s="2"/>
+      <c r="R3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF3" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AG3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH3" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="L3" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="P3" s="2"/>
-      <c r="Q3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE3" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG3" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH3" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="AI3" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
+      </c>
+      <c r="AK3" t="s" s="2">
+        <v>86</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="L4" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="M4" s="2"/>
+      <c r="M4" t="s" s="2">
+        <v>89</v>
+      </c>
       <c r="N4" s="2"/>
-      <c r="O4" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="P4" s="2"/>
-      <c r="Q4" t="s" s="2">
-        <v>74</v>
-      </c>
+      <c r="O4" s="2"/>
+      <c r="P4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
+      </c>
+      <c r="AK4" t="s" s="2">
+        <v>75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="M5" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="N5" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="O5" s="2"/>
+      <c r="P5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q5" s="2"/>
+      <c r="R5" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="S5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF5" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L5" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="N5" s="2"/>
-      <c r="O5" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="P5" s="2"/>
-      <c r="Q5" t="s" s="2">
-        <v>3</v>
-      </c>
-      <c r="R5" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S5" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T5" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U5" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V5" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W5" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X5" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y5" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z5" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA5" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB5" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC5" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD5" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE5" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AF5" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AG5" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
+      </c>
+      <c r="AK5" t="s" s="2">
+        <v>100</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K6" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M6" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q6" s="2"/>
+      <c r="R6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF6" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AG6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH6" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK6" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="K6" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L6" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="P6" s="2"/>
-      <c r="Q6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG6" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI6" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ6" t="s" s="2">
-        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-18T12:02:45+00:00</t>
+    <t>2023-04-24T21:40:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-24T21:40:58+00:00</t>
+    <t>2023-04-25T17:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-25T17:34:53+00:00</t>
+    <t>2023-04-30T20:59:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T20:59:20+00:00</t>
+    <t>2023-04-30T21:23:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T21:23:00+00:00</t>
+    <t>2023-05-05T00:02:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>3.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T00:02:52+00:00</t>
+    <t>2023-11-28T12:13:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -126,7 +126,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:Element</t>
+    <t>element:Condition</t>
   </si>
   <si>
     <t>ID</t>
@@ -257,6 +257,10 @@
 </t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>Extension.id</t>
   </si>
   <si>
@@ -300,10 +304,6 @@
   </si>
   <si>
     <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Extension.url</t>
@@ -461,10 +461,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -900,7 +900,7 @@
         <v>79</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>75</v>
@@ -908,10 +908,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -922,7 +922,7 @@
         <v>76</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>75</v>
@@ -934,13 +934,13 @@
         <v>75</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -991,13 +991,13 @@
         <v>75</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>75</v>
@@ -1006,15 +1006,15 @@
         <v>75</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1037,13 +1037,13 @@
         <v>75</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>29</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1082,19 +1082,19 @@
         <v>75</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>76</v>
@@ -1106,7 +1106,7 @@
         <v>75</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>75</v>
@@ -1125,10 +1125,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>75</v>
@@ -1202,10 +1202,10 @@
         <v>95</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>75</v>
@@ -1233,7 +1233,7 @@
         <v>76</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>75</v>
@@ -1308,7 +1308,7 @@
         <v>76</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>75</v>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:13:03+00:00</t>
+    <t>2023-11-30T13:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-30T13:40:49+00:00</t>
+    <t>2023-11-30T14:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-30T14:55:40+00:00</t>
+    <t>2023-12-01T12:31:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -45,7 +45,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-01T12:31:40+00:00</t>
+    <t>2023-12-01T13:42:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-01T13:42:49+00:00</t>
+    <t>2023-12-19T10:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:28:26+00:00</t>
+    <t>2023-12-19T10:34:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:34:37+00:00</t>
+    <t>2024-01-06T18:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -45,7 +45,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-06T18:57:36+00:00</t>
+    <t>2024-01-08T22:02:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:06+00:00</t>
+    <t>2024-01-08T22:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:40+00:00</t>
+    <t>2024-03-19T10:43:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-19T10:43:29+00:00</t>
+    <t>2024-04-03T07:46:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:46:18+00:00</t>
+    <t>2024-04-03T10:16:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T10:16:02+00:00</t>
+    <t>2024-04-10T06:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -66,7 +66,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>HL7 Denmark (http://www.hl7.dk, jenskristianvilladsen@gmail.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T06:34:41+00:00</t>
+    <t>2024-04-11T09:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-11T09:53:59+00:00</t>
+    <t>2024-04-12T06:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T06:23:14+00:00</t>
+    <t>2024-04-16T10:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-16T10:58:26+00:00</t>
+    <t>2024-04-18T15:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:20:26+00:00</t>
+    <t>2024-04-18T15:27:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:27:51+00:00</t>
+    <t>2024-04-22T11:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T11:01:11+00:00</t>
+    <t>2024-04-22T12:03:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T12:03:36+00:00</t>
+    <t>2024-04-22T13:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T13:38:01+00:00</t>
+    <t>2024-04-23T08:24:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T08:24:27+00:00</t>
+    <t>2024-04-23T10:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T10:50:14+00:00</t>
+    <t>2024-04-23T18:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T18:15:55+00:00</t>
+    <t>2024-05-02T12:47:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-02T12:47:39+00:00</t>
+    <t>2024-05-03T13:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -45,7 +45,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T13:03:24+00:00</t>
+    <t>2024-05-06T06:35:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T06:35:09+00:00</t>
+    <t>2024-05-06T07:49:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.2.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T07:49:19+00:00</t>
+    <t>2024-05-06T14:14:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T14:14:33+00:00</t>
+    <t>2024-05-10T08:40:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T08:40:47+00:00</t>
+    <t>2024-05-10T19:12:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T19:12:38+00:00</t>
+    <t>2024-05-12T08:40:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:40:34+00:00</t>
+    <t>2024-05-12T08:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:41:58+00:00</t>
+    <t>2024-05-12T09:45:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T09:45:49+00:00</t>
+    <t>2024-05-12T11:37:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T11:37:02+00:00</t>
+    <t>2024-06-03T20:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T20:51:53+00:00</t>
+    <t>2024-06-25T21:12:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:12:53+00:00</t>
+    <t>2024-06-25T21:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:21:07+00:00</t>
+    <t>2024-06-25T21:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:20:43+00:00</t>
+    <t>2024-06-25T21:42:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:42:34+00:00</t>
+    <t>2024-06-26T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-26T14:36:19+00:00</t>
+    <t>2024-06-27T10:47:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-27T10:47:07+00:00</t>
+    <t>2024-08-11T15:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-11T15:57:41+00:00</t>
+    <t>2024-10-17T12:12:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:12:58+00:00</t>
+    <t>2024-10-17T12:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:15:17+00:00</t>
+    <t>2024-10-18T06:07:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T06:07:37+00:00</t>
+    <t>2024-10-27T12:31:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T12:31:37+00:00</t>
+    <t>2024-11-04T14:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:15:57+00:00</t>
+    <t>2024-11-04T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:58:42+00:00</t>
+    <t>2024-11-04T15:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T15:07:28+00:00</t>
+    <t>2024-11-05T12:45:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.4.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T12:45:46+00:00</t>
+    <t>2024-11-15T12:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T12:49:28+00:00</t>
+    <t>2024-11-15T13:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T13:03:47+00:00</t>
+    <t>2024-11-29T07:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T07:41:39+00:00</t>
+    <t>2024-11-29T10:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T10:20:07+00:00</t>
+    <t>2024-12-11T08:38:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -45,7 +45,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T08:38:49+00:00</t>
+    <t>2024-12-11T09:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T09:50:58+00:00</t>
+    <t>2024-12-16T15:09:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:09:03+00:00</t>
+    <t>2024-12-16T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ConditionLastAssertedDate.xlsx
+++ b/StructureDefinition-ConditionLastAssertedDate.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:16:17+00:00</t>
+    <t>2024-12-16T15:31:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
